--- a/Project/DiceWarrior/LubanTool/Datas/奖励项.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/奖励项.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView/>
+    <workbookView windowHeight="17470"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -35,10 +35,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>rewardType</t>
-  </si>
-  <si>
-    <t>parameter</t>
+    <t>bagId</t>
+  </si>
+  <si>
+    <t>num</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>des</t>
   </si>
   <si>
     <t>##type</t>
@@ -47,6 +53,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -56,7 +65,25 @@
     <t>##</t>
   </si>
   <si>
-    <t>钱</t>
+    <t>物品表id</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>少量金币</t>
+  </si>
+  <si>
+    <t>大量金币</t>
   </si>
 </sst>
 </file>
@@ -69,10 +96,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -222,7 +257,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,6 +266,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor theme="4" tint="0.599993896298105"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -416,11 +469,115 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -542,139 +699,172 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1201,178 +1391,346 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="25" customHeight="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="2" width="8.72727272727273" style="1"/>
+    <col min="3" max="5" width="16.5454545454545" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32.0909090909091" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.72727272727273" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" customHeight="1" spans="1:6">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:6">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:6">
+      <c r="A3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:6">
+      <c r="A4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:6">
+      <c r="A5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:6">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9">
+        <v>2</v>
+      </c>
+      <c r="D6" s="9">
+        <v>10</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:6">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7">
+        <v>2</v>
+      </c>
+      <c r="C7" s="7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="7">
+        <v>30</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:6">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9">
+        <v>3</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>100</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:6">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:6">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:6">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:6">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:6">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:6">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9">
         <v>9</v>
       </c>
-      <c r="D6">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:6">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7">
+        <v>10</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:6">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9">
+        <v>11</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:6">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7">
+        <v>12</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:6">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9">
+        <v>13</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:6">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7">
+        <v>14</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:6">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9">
+        <v>15</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:6">
+      <c r="A21" s="6"/>
+      <c r="B21" s="7">
+        <v>16</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:6">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9">
+        <v>17</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:6">
+      <c r="A23" s="6"/>
+      <c r="B23" s="7">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:6">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9">
+        <v>19</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:6">
+      <c r="A25" s="6"/>
+      <c r="B25" s="7">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="B9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="B10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="B13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="B14">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="B15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="B16">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26">
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:6">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9">
         <v>21</v>
       </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27">
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:6">
+      <c r="A27" s="6"/>
+      <c r="B27" s="7">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28">
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:6">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11">
         <v>23</v>
       </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Project/DiceWarrior/LubanTool/Datas/奖励项.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/奖励项.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\ProjectDiceWarrior\Project\DiceWarrior\LubanTool\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17470"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="219">
   <si>
     <t>##var</t>
   </si>
@@ -84,6 +89,606 @@
   </si>
   <si>
     <t>大量金币</t>
+  </si>
+  <si>
+    <t>素白渐变素彩蛋</t>
+  </si>
+  <si>
+    <t>Egg 01A：素白配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>琥珀渐变素彩蛋</t>
+  </si>
+  <si>
+    <t>Egg 01B：琥珀配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>蔷薇渐变素彩蛋</t>
+  </si>
+  <si>
+    <t>Egg 01C：蔷薇配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>青碧渐变素彩蛋</t>
+  </si>
+  <si>
+    <t>Egg 01D：青碧配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>靛蓝渐变素彩蛋</t>
+  </si>
+  <si>
+    <t>Egg 01E：靛蓝配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>金黄山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02A：金黄配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫青山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02B：紫青配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>绯红山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02C：绯红配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>珊瑚山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02D：珊瑚配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>象牙山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02E：象牙配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>桃粉彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03A：桃粉配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>晴蓝彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03B：晴蓝配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>金橙彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03C：金橙配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>玫红彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03D：玫红配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>霓紫彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03E：霓紫配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>薄荷横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04A：薄荷配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>玫棕横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04B：玫棕配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>海蓝横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04C：海蓝配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>翠绿横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04D：翠绿配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫罗兰横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04E：紫罗兰配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>猩红熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05A：猩红配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>橙紫熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05B：橙紫配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>柠檬熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05C：柠檬配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>青黛熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05D：青黛配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>暗红熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05E：暗红配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>烈焰闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06A：烈焰配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>铜棕闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06B：铜棕配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>荧黄闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06C：荧黄配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>碧绿闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06D：碧绿配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫晶闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06E：紫晶配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>橙绿徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07A：橙绿配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>莓果徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07B：莓果配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫金徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07C：紫金配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>明黄徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07D：明黄配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>柠青徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07E：柠青配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>粉灰碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08A：粉灰配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>薰衣草碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08B：薰衣草配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>雾蓝碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08C：雾蓝配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>深海碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08D：深海配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>墨黑碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08E：墨黑配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>金黄顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09A：金黄配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>荧绿顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09B：荧绿配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>青蓝顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09C：青蓝配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫晶顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09D：紫晶配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>珊瑚顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09E：珊瑚配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>莓红宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10A：莓红配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>翡翠宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10B：翡翠配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>青紫宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10C：青紫配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>金黄宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10D：金黄配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>玫紫宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10E：玫紫配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>南瓜南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11A：南瓜配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>朱红南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11B：朱红配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫莓南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11C：紫莓配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>青柠南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11D：青柠配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>雪白南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11E：雪白配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>莓粉圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12A：莓粉配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>蔚蓝圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12B：蔚蓝配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>青柠圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12C：青柠配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>黄绿圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12D：黄绿配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>青紫圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12E：青紫配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>翡翠菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13A：翡翠配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>珊瑚菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13B：珊瑚配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫罗兰菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13C：紫罗兰配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>晴蓝菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13D：晴蓝配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>莓红菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13E：莓红配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫金金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14A：紫金配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>深青金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14B：深青配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>玫红金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14C：玫红配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>橙金金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14D：橙金配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>翠绿金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14E：翠绿配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>蓝紫宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15A：蓝紫配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>玫粉宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15B：玫粉配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>绯红宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15C：绯红配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>金蓝宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15D：金蓝配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>翡翠宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15E：翡翠配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>铜焰暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16A：铜焰配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>翠焰暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16B：翠焰配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫焰暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16C：紫焰配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>幽紫暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16D：幽紫配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>琥珀暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16E：琥珀配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>幽紫灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17A：幽紫配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>午夜蓝灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17B：午夜蓝配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>青绿灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17C：青绿配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>棕橙灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17D：棕橙配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>灰黑灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17E：灰黑配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫黑熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18A：紫黑配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>靛蓝熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18B：靛蓝配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>深青熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18C：深青配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>棕红熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18D：棕红配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>草绿熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18E：草绿配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫蓝锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19A：紫蓝配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>森林绿锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19B：森林绿配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>金沙锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19C：金沙配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>海蓝锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19D：海蓝配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>莓紫锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19E：莓紫配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>紫粉花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20A：紫粉配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>靛红花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20B：靛红配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>杏绿花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20C：杏绿配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>香槟花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20D：香槟配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>青翠花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20E：青翠配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
   </si>
 </sst>
 </file>
@@ -96,13 +701,12 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -110,30 +714,24 @@
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -141,15 +739,13 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -157,7 +753,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -165,7 +760,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -173,88 +767,70 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="36">
@@ -332,19 +908,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -356,19 +932,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +956,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +980,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +1004,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,24 +1028,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -502,6 +1078,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="0"/>
@@ -521,6 +1108,19 @@
       <right style="thin">
         <color theme="0"/>
       </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
       <top style="thick">
         <color theme="0"/>
       </top>
@@ -558,6 +1158,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="0"/>
@@ -575,6 +1188,17 @@
       <right style="thin">
         <color theme="0"/>
       </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
       <top style="thin">
         <color theme="0"/>
       </top>
@@ -610,7 +1234,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -705,7 +1329,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -717,34 +1341,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -759,10 +1383,10 @@
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -771,10 +1395,10 @@
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -783,10 +1407,10 @@
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -795,10 +1419,10 @@
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -807,10 +1431,10 @@
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -819,17 +1443,17 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -842,28 +1466,58 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1182,76 +1836,16 @@
         <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="WPS">
@@ -1275,9 +1869,7 @@
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr"/>
@@ -1287,27 +1879,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:gradFill>
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
+                <a:schemeClr val="phClr"/>
               </a:gs>
               <a:gs pos="100000">
                 <a:schemeClr val="phClr"/>
@@ -1316,7 +1904,6 @@
             <a:lin ang="2700000" scaled="1"/>
           </a:gradFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1359,17 +1946,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1391,16 +1978,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="25" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="A1:K129"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="8.72727272727273" style="1"/>
-    <col min="3" max="5" width="16.5454545454545" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32.0909090909091" style="1" customWidth="1"/>
+    <col min="3" max="4" width="16.5454545454545" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5454545454545" style="1" customWidth="1"/>
+    <col min="6" max="6" width="81.5454545454545" style="1" customWidth="1"/>
     <col min="7" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:6">
+    <row r="1" ht="25" customHeight="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1419,321 +2007,2774 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:11">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:6">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:11">
+      <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:6">
-      <c r="A4" s="8" t="s">
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:11">
+      <c r="A4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:6">
-      <c r="A5" s="6" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="14"/>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:11">
+      <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:6">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9">
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="11"/>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:11">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13">
+        <v>1</v>
+      </c>
+      <c r="C6" s="13">
         <v>2</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="13">
         <v>10</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:6">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7">
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:11">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10">
         <v>2</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="10">
         <v>2</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="10">
         <v>30</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:6">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9">
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="11"/>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:11">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13">
         <v>3</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="13">
         <v>2</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="13">
         <v>100</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:6">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7">
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="14"/>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:11">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10">
         <v>4</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:6">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="11"/>
+    </row>
+    <row r="10" ht="25" customHeight="1" spans="1:11">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13">
         <v>5</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:6">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7">
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="14"/>
+    </row>
+    <row r="11" ht="25" customHeight="1" spans="1:11">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10">
         <v>6</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:6">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="11"/>
+    </row>
+    <row r="12" ht="25" customHeight="1" spans="1:11">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13">
         <v>7</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:6">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="14"/>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:11">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10">
         <v>8</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:6">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9">
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" ht="25" customHeight="1" spans="1:11">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13">
         <v>9</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:6">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="14"/>
+    </row>
+    <row r="15" ht="25" customHeight="1" spans="1:11">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10">
         <v>10</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:6">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9">
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" ht="25" customHeight="1" spans="1:11">
+      <c r="A16" s="12"/>
+      <c r="B16" s="13">
         <v>11</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:6">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="14"/>
+    </row>
+    <row r="17" ht="25" customHeight="1" spans="1:11">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10">
         <v>12</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:6">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" ht="25" customHeight="1" spans="1:11">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13">
         <v>13</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:6">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="19" ht="25" customHeight="1" spans="1:11">
+      <c r="A19" s="9"/>
+      <c r="B19" s="10">
         <v>14</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:6">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9">
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" ht="25" customHeight="1" spans="1:11">
+      <c r="A20" s="12"/>
+      <c r="B20" s="13">
         <v>15</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:6">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7">
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="14"/>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10">
         <v>16</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:6">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="11"/>
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:11">
+      <c r="A22" s="12"/>
+      <c r="B22" s="13">
         <v>17</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:6">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:11">
+      <c r="A23" s="9"/>
+      <c r="B23" s="10">
         <v>18</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:6">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9">
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" ht="25" customHeight="1" spans="1:11">
+      <c r="A24" s="12"/>
+      <c r="B24" s="13">
         <v>19</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:6">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7">
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="14"/>
+    </row>
+    <row r="25" ht="25" customHeight="1" spans="1:11">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10">
         <v>20</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:6">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" ht="25" customHeight="1" spans="1:11">
+      <c r="A26" s="12"/>
+      <c r="B26" s="13">
         <v>21</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:6">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7">
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="14"/>
+    </row>
+    <row r="27" ht="25" customHeight="1" spans="1:11">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10">
         <v>22</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:6">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11">
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" ht="25" customHeight="1" spans="1:11">
+      <c r="A28" s="12"/>
+      <c r="B28" s="13">
         <v>23</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="14"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="15"/>
+      <c r="B29" s="16">
+        <v>10001</v>
+      </c>
+      <c r="C29" s="16">
+        <v>10001</v>
+      </c>
+      <c r="D29" s="16">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="17"/>
+      <c r="B30" s="18">
+        <v>10002</v>
+      </c>
+      <c r="C30" s="18">
+        <v>10002</v>
+      </c>
+      <c r="D30" s="18">
+        <v>1</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="14"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="15"/>
+      <c r="B31" s="16">
+        <v>10003</v>
+      </c>
+      <c r="C31" s="16">
+        <v>10003</v>
+      </c>
+      <c r="D31" s="16">
+        <v>1</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="17"/>
+      <c r="B32" s="18">
+        <v>10004</v>
+      </c>
+      <c r="C32" s="18">
+        <v>10004</v>
+      </c>
+      <c r="D32" s="18">
+        <v>1</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="14"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="15"/>
+      <c r="B33" s="16">
+        <v>10005</v>
+      </c>
+      <c r="C33" s="16">
+        <v>10005</v>
+      </c>
+      <c r="D33" s="16">
+        <v>1</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="17"/>
+      <c r="B34" s="18">
+        <v>10006</v>
+      </c>
+      <c r="C34" s="18">
+        <v>10006</v>
+      </c>
+      <c r="D34" s="18">
+        <v>1</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="14"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="15"/>
+      <c r="B35" s="16">
+        <v>10007</v>
+      </c>
+      <c r="C35" s="16">
+        <v>10007</v>
+      </c>
+      <c r="D35" s="16">
+        <v>1</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="11"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="17"/>
+      <c r="B36" s="18">
+        <v>10008</v>
+      </c>
+      <c r="C36" s="18">
+        <v>10008</v>
+      </c>
+      <c r="D36" s="18">
+        <v>1</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="14"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="15"/>
+      <c r="B37" s="16">
+        <v>10009</v>
+      </c>
+      <c r="C37" s="16">
+        <v>10009</v>
+      </c>
+      <c r="D37" s="16">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="11"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="17"/>
+      <c r="B38" s="18">
+        <v>10010</v>
+      </c>
+      <c r="C38" s="18">
+        <v>10010</v>
+      </c>
+      <c r="D38" s="18">
+        <v>1</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="14"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="15"/>
+      <c r="B39" s="16">
+        <v>10011</v>
+      </c>
+      <c r="C39" s="16">
+        <v>10011</v>
+      </c>
+      <c r="D39" s="16">
+        <v>1</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="11"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="17"/>
+      <c r="B40" s="18">
+        <v>10012</v>
+      </c>
+      <c r="C40" s="18">
+        <v>10012</v>
+      </c>
+      <c r="D40" s="18">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="14"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="15"/>
+      <c r="B41" s="16">
+        <v>10013</v>
+      </c>
+      <c r="C41" s="16">
+        <v>10013</v>
+      </c>
+      <c r="D41" s="16">
+        <v>1</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="11"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="17"/>
+      <c r="B42" s="18">
+        <v>10014</v>
+      </c>
+      <c r="C42" s="18">
+        <v>10014</v>
+      </c>
+      <c r="D42" s="18">
+        <v>1</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="14"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="15"/>
+      <c r="B43" s="16">
+        <v>10015</v>
+      </c>
+      <c r="C43" s="16">
+        <v>10015</v>
+      </c>
+      <c r="D43" s="16">
+        <v>1</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="11"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="17"/>
+      <c r="B44" s="18">
+        <v>10016</v>
+      </c>
+      <c r="C44" s="18">
+        <v>10016</v>
+      </c>
+      <c r="D44" s="18">
+        <v>1</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="14"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="15"/>
+      <c r="B45" s="16">
+        <v>10017</v>
+      </c>
+      <c r="C45" s="16">
+        <v>10017</v>
+      </c>
+      <c r="D45" s="16">
+        <v>1</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="11"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="17"/>
+      <c r="B46" s="18">
+        <v>10018</v>
+      </c>
+      <c r="C46" s="18">
+        <v>10018</v>
+      </c>
+      <c r="D46" s="18">
+        <v>1</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="14"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="15"/>
+      <c r="B47" s="16">
+        <v>10019</v>
+      </c>
+      <c r="C47" s="16">
+        <v>10019</v>
+      </c>
+      <c r="D47" s="16">
+        <v>1</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="11"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="17"/>
+      <c r="B48" s="18">
+        <v>10020</v>
+      </c>
+      <c r="C48" s="18">
+        <v>10020</v>
+      </c>
+      <c r="D48" s="18">
+        <v>1</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="14"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="15"/>
+      <c r="B49" s="16">
+        <v>10021</v>
+      </c>
+      <c r="C49" s="16">
+        <v>10021</v>
+      </c>
+      <c r="D49" s="16">
+        <v>1</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="11"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="17"/>
+      <c r="B50" s="18">
+        <v>10022</v>
+      </c>
+      <c r="C50" s="18">
+        <v>10022</v>
+      </c>
+      <c r="D50" s="18">
+        <v>1</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="14"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="15"/>
+      <c r="B51" s="16">
+        <v>10023</v>
+      </c>
+      <c r="C51" s="16">
+        <v>10023</v>
+      </c>
+      <c r="D51" s="16">
+        <v>1</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="11"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="17"/>
+      <c r="B52" s="18">
+        <v>10024</v>
+      </c>
+      <c r="C52" s="18">
+        <v>10024</v>
+      </c>
+      <c r="D52" s="18">
+        <v>1</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="14"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="15"/>
+      <c r="B53" s="16">
+        <v>10025</v>
+      </c>
+      <c r="C53" s="16">
+        <v>10025</v>
+      </c>
+      <c r="D53" s="16">
+        <v>1</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="11"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="17"/>
+      <c r="B54" s="18">
+        <v>10026</v>
+      </c>
+      <c r="C54" s="18">
+        <v>10026</v>
+      </c>
+      <c r="D54" s="18">
+        <v>1</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="14"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="15"/>
+      <c r="B55" s="16">
+        <v>10027</v>
+      </c>
+      <c r="C55" s="16">
+        <v>10027</v>
+      </c>
+      <c r="D55" s="16">
+        <v>1</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="11"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="17"/>
+      <c r="B56" s="18">
+        <v>10028</v>
+      </c>
+      <c r="C56" s="18">
+        <v>10028</v>
+      </c>
+      <c r="D56" s="18">
+        <v>1</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="14"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="15"/>
+      <c r="B57" s="16">
+        <v>10029</v>
+      </c>
+      <c r="C57" s="16">
+        <v>10029</v>
+      </c>
+      <c r="D57" s="16">
+        <v>1</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="11"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="17"/>
+      <c r="B58" s="18">
+        <v>10030</v>
+      </c>
+      <c r="C58" s="18">
+        <v>10030</v>
+      </c>
+      <c r="D58" s="18">
+        <v>1</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="14"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="15"/>
+      <c r="B59" s="16">
+        <v>10031</v>
+      </c>
+      <c r="C59" s="16">
+        <v>10031</v>
+      </c>
+      <c r="D59" s="16">
+        <v>1</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="11"/>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="17"/>
+      <c r="B60" s="18">
+        <v>10032</v>
+      </c>
+      <c r="C60" s="18">
+        <v>10032</v>
+      </c>
+      <c r="D60" s="18">
+        <v>1</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="14"/>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="15"/>
+      <c r="B61" s="16">
+        <v>10033</v>
+      </c>
+      <c r="C61" s="16">
+        <v>10033</v>
+      </c>
+      <c r="D61" s="16">
+        <v>1</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="11"/>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="17"/>
+      <c r="B62" s="18">
+        <v>10034</v>
+      </c>
+      <c r="C62" s="18">
+        <v>10034</v>
+      </c>
+      <c r="D62" s="18">
+        <v>1</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="14"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="15"/>
+      <c r="B63" s="16">
+        <v>10035</v>
+      </c>
+      <c r="C63" s="16">
+        <v>10035</v>
+      </c>
+      <c r="D63" s="16">
+        <v>1</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G63" s="10"/>
+      <c r="H63" s="10"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="11"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="17"/>
+      <c r="B64" s="18">
+        <v>10036</v>
+      </c>
+      <c r="C64" s="18">
+        <v>10036</v>
+      </c>
+      <c r="D64" s="18">
+        <v>1</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="14"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="15"/>
+      <c r="B65" s="16">
+        <v>10037</v>
+      </c>
+      <c r="C65" s="16">
+        <v>10037</v>
+      </c>
+      <c r="D65" s="16">
+        <v>1</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G65" s="10"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="11"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="17"/>
+      <c r="B66" s="18">
+        <v>10038</v>
+      </c>
+      <c r="C66" s="18">
+        <v>10038</v>
+      </c>
+      <c r="D66" s="18">
+        <v>1</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="14"/>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="15"/>
+      <c r="B67" s="16">
+        <v>10039</v>
+      </c>
+      <c r="C67" s="16">
+        <v>10039</v>
+      </c>
+      <c r="D67" s="16">
+        <v>1</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="11"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="17"/>
+      <c r="B68" s="18">
+        <v>10040</v>
+      </c>
+      <c r="C68" s="18">
+        <v>10040</v>
+      </c>
+      <c r="D68" s="18">
+        <v>1</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="14"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="15"/>
+      <c r="B69" s="16">
+        <v>10041</v>
+      </c>
+      <c r="C69" s="16">
+        <v>10041</v>
+      </c>
+      <c r="D69" s="16">
+        <v>1</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G69" s="10"/>
+      <c r="H69" s="10"/>
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="11"/>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="17"/>
+      <c r="B70" s="18">
+        <v>10042</v>
+      </c>
+      <c r="C70" s="18">
+        <v>10042</v>
+      </c>
+      <c r="D70" s="18">
+        <v>1</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="14"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="15"/>
+      <c r="B71" s="16">
+        <v>10043</v>
+      </c>
+      <c r="C71" s="16">
+        <v>10043</v>
+      </c>
+      <c r="D71" s="16">
+        <v>1</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F71" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="11"/>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="17"/>
+      <c r="B72" s="18">
+        <v>10044</v>
+      </c>
+      <c r="C72" s="18">
+        <v>10044</v>
+      </c>
+      <c r="D72" s="18">
+        <v>1</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="14"/>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="15"/>
+      <c r="B73" s="16">
+        <v>10045</v>
+      </c>
+      <c r="C73" s="16">
+        <v>10045</v>
+      </c>
+      <c r="D73" s="16">
+        <v>1</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="G73" s="10"/>
+      <c r="H73" s="10"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="11"/>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="17"/>
+      <c r="B74" s="18">
+        <v>10046</v>
+      </c>
+      <c r="C74" s="18">
+        <v>10046</v>
+      </c>
+      <c r="D74" s="18">
+        <v>1</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="14"/>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="15"/>
+      <c r="B75" s="16">
+        <v>10047</v>
+      </c>
+      <c r="C75" s="16">
+        <v>10047</v>
+      </c>
+      <c r="D75" s="16">
+        <v>1</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F75" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="G75" s="10"/>
+      <c r="H75" s="10"/>
+      <c r="I75" s="10"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="11"/>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="17"/>
+      <c r="B76" s="18">
+        <v>10048</v>
+      </c>
+      <c r="C76" s="18">
+        <v>10048</v>
+      </c>
+      <c r="D76" s="18">
+        <v>1</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="13"/>
+      <c r="K76" s="14"/>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="15"/>
+      <c r="B77" s="16">
+        <v>10049</v>
+      </c>
+      <c r="C77" s="16">
+        <v>10049</v>
+      </c>
+      <c r="D77" s="16">
+        <v>1</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G77" s="10"/>
+      <c r="H77" s="10"/>
+      <c r="I77" s="10"/>
+      <c r="J77" s="10"/>
+      <c r="K77" s="11"/>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="17"/>
+      <c r="B78" s="18">
+        <v>10050</v>
+      </c>
+      <c r="C78" s="18">
+        <v>10050</v>
+      </c>
+      <c r="D78" s="18">
+        <v>1</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F78" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+      <c r="K78" s="14"/>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="15"/>
+      <c r="B79" s="16">
+        <v>10051</v>
+      </c>
+      <c r="C79" s="16">
+        <v>10051</v>
+      </c>
+      <c r="D79" s="16">
+        <v>1</v>
+      </c>
+      <c r="E79" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G79" s="10"/>
+      <c r="H79" s="10"/>
+      <c r="I79" s="10"/>
+      <c r="J79" s="10"/>
+      <c r="K79" s="11"/>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="17"/>
+      <c r="B80" s="18">
+        <v>10052</v>
+      </c>
+      <c r="C80" s="18">
+        <v>10052</v>
+      </c>
+      <c r="D80" s="18">
+        <v>1</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
+      <c r="K80" s="14"/>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="15"/>
+      <c r="B81" s="16">
+        <v>10053</v>
+      </c>
+      <c r="C81" s="16">
+        <v>10053</v>
+      </c>
+      <c r="D81" s="16">
+        <v>1</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="G81" s="10"/>
+      <c r="H81" s="10"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="11"/>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="17"/>
+      <c r="B82" s="18">
+        <v>10054</v>
+      </c>
+      <c r="C82" s="18">
+        <v>10054</v>
+      </c>
+      <c r="D82" s="18">
+        <v>1</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="14"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="15"/>
+      <c r="B83" s="16">
+        <v>10055</v>
+      </c>
+      <c r="C83" s="16">
+        <v>10055</v>
+      </c>
+      <c r="D83" s="16">
+        <v>1</v>
+      </c>
+      <c r="E83" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F83" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="G83" s="10"/>
+      <c r="H83" s="10"/>
+      <c r="I83" s="10"/>
+      <c r="J83" s="10"/>
+      <c r="K83" s="11"/>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="17"/>
+      <c r="B84" s="18">
+        <v>10056</v>
+      </c>
+      <c r="C84" s="18">
+        <v>10056</v>
+      </c>
+      <c r="D84" s="18">
+        <v>1</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13"/>
+      <c r="K84" s="14"/>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="15"/>
+      <c r="B85" s="16">
+        <v>10057</v>
+      </c>
+      <c r="C85" s="16">
+        <v>10057</v>
+      </c>
+      <c r="D85" s="16">
+        <v>1</v>
+      </c>
+      <c r="E85" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F85" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G85" s="10"/>
+      <c r="H85" s="10"/>
+      <c r="I85" s="10"/>
+      <c r="J85" s="10"/>
+      <c r="K85" s="11"/>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="17"/>
+      <c r="B86" s="18">
+        <v>10058</v>
+      </c>
+      <c r="C86" s="18">
+        <v>10058</v>
+      </c>
+      <c r="D86" s="18">
+        <v>1</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+      <c r="K86" s="14"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="15"/>
+      <c r="B87" s="16">
+        <v>10059</v>
+      </c>
+      <c r="C87" s="16">
+        <v>10059</v>
+      </c>
+      <c r="D87" s="16">
+        <v>1</v>
+      </c>
+      <c r="E87" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="G87" s="10"/>
+      <c r="H87" s="10"/>
+      <c r="I87" s="10"/>
+      <c r="J87" s="10"/>
+      <c r="K87" s="11"/>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="17"/>
+      <c r="B88" s="18">
+        <v>10060</v>
+      </c>
+      <c r="C88" s="18">
+        <v>10060</v>
+      </c>
+      <c r="D88" s="18">
+        <v>1</v>
+      </c>
+      <c r="E88" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F88" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
+      <c r="J88" s="13"/>
+      <c r="K88" s="14"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="15"/>
+      <c r="B89" s="16">
+        <v>10061</v>
+      </c>
+      <c r="C89" s="16">
+        <v>10061</v>
+      </c>
+      <c r="D89" s="16">
+        <v>1</v>
+      </c>
+      <c r="E89" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F89" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="G89" s="10"/>
+      <c r="H89" s="10"/>
+      <c r="I89" s="10"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="11"/>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="17"/>
+      <c r="B90" s="18">
+        <v>10062</v>
+      </c>
+      <c r="C90" s="18">
+        <v>10062</v>
+      </c>
+      <c r="D90" s="18">
+        <v>1</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F90" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
+      <c r="K90" s="14"/>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="15"/>
+      <c r="B91" s="16">
+        <v>10063</v>
+      </c>
+      <c r="C91" s="16">
+        <v>10063</v>
+      </c>
+      <c r="D91" s="16">
+        <v>1</v>
+      </c>
+      <c r="E91" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="F91" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="G91" s="10"/>
+      <c r="H91" s="10"/>
+      <c r="I91" s="10"/>
+      <c r="J91" s="10"/>
+      <c r="K91" s="11"/>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="17"/>
+      <c r="B92" s="18">
+        <v>10064</v>
+      </c>
+      <c r="C92" s="18">
+        <v>10064</v>
+      </c>
+      <c r="D92" s="18">
+        <v>1</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F92" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="13"/>
+      <c r="J92" s="13"/>
+      <c r="K92" s="14"/>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="15"/>
+      <c r="B93" s="16">
+        <v>10065</v>
+      </c>
+      <c r="C93" s="16">
+        <v>10065</v>
+      </c>
+      <c r="D93" s="16">
+        <v>1</v>
+      </c>
+      <c r="E93" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F93" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="G93" s="10"/>
+      <c r="H93" s="10"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="10"/>
+      <c r="K93" s="11"/>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="17"/>
+      <c r="B94" s="18">
+        <v>10066</v>
+      </c>
+      <c r="C94" s="18">
+        <v>10066</v>
+      </c>
+      <c r="D94" s="18">
+        <v>1</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F94" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="13"/>
+      <c r="J94" s="13"/>
+      <c r="K94" s="14"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="15"/>
+      <c r="B95" s="16">
+        <v>10067</v>
+      </c>
+      <c r="C95" s="16">
+        <v>10067</v>
+      </c>
+      <c r="D95" s="16">
+        <v>1</v>
+      </c>
+      <c r="E95" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="F95" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="G95" s="10"/>
+      <c r="H95" s="10"/>
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="11"/>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="17"/>
+      <c r="B96" s="18">
+        <v>10068</v>
+      </c>
+      <c r="C96" s="18">
+        <v>10068</v>
+      </c>
+      <c r="D96" s="18">
+        <v>1</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="13"/>
+      <c r="J96" s="13"/>
+      <c r="K96" s="14"/>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="15"/>
+      <c r="B97" s="16">
+        <v>10069</v>
+      </c>
+      <c r="C97" s="16">
+        <v>10069</v>
+      </c>
+      <c r="D97" s="16">
+        <v>1</v>
+      </c>
+      <c r="E97" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F97" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="G97" s="10"/>
+      <c r="H97" s="10"/>
+      <c r="I97" s="10"/>
+      <c r="J97" s="10"/>
+      <c r="K97" s="11"/>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="17"/>
+      <c r="B98" s="18">
+        <v>10070</v>
+      </c>
+      <c r="C98" s="18">
+        <v>10070</v>
+      </c>
+      <c r="D98" s="18">
+        <v>1</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G98" s="13"/>
+      <c r="H98" s="13"/>
+      <c r="I98" s="13"/>
+      <c r="J98" s="13"/>
+      <c r="K98" s="14"/>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="15"/>
+      <c r="B99" s="16">
+        <v>10071</v>
+      </c>
+      <c r="C99" s="16">
+        <v>10071</v>
+      </c>
+      <c r="D99" s="16">
+        <v>1</v>
+      </c>
+      <c r="E99" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="F99" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="G99" s="10"/>
+      <c r="H99" s="10"/>
+      <c r="I99" s="10"/>
+      <c r="J99" s="10"/>
+      <c r="K99" s="11"/>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="17"/>
+      <c r="B100" s="18">
+        <v>10072</v>
+      </c>
+      <c r="C100" s="18">
+        <v>10072</v>
+      </c>
+      <c r="D100" s="18">
+        <v>1</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F100" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="13"/>
+      <c r="J100" s="13"/>
+      <c r="K100" s="14"/>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="15"/>
+      <c r="B101" s="16">
+        <v>10073</v>
+      </c>
+      <c r="C101" s="16">
+        <v>10073</v>
+      </c>
+      <c r="D101" s="16">
+        <v>1</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="F101" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="G101" s="10"/>
+      <c r="H101" s="10"/>
+      <c r="I101" s="10"/>
+      <c r="J101" s="10"/>
+      <c r="K101" s="11"/>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="17"/>
+      <c r="B102" s="18">
+        <v>10074</v>
+      </c>
+      <c r="C102" s="18">
+        <v>10074</v>
+      </c>
+      <c r="D102" s="18">
+        <v>1</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="F102" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="13"/>
+      <c r="K102" s="14"/>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="15"/>
+      <c r="B103" s="16">
+        <v>10075</v>
+      </c>
+      <c r="C103" s="16">
+        <v>10075</v>
+      </c>
+      <c r="D103" s="16">
+        <v>1</v>
+      </c>
+      <c r="E103" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F103" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="G103" s="10"/>
+      <c r="H103" s="10"/>
+      <c r="I103" s="10"/>
+      <c r="J103" s="10"/>
+      <c r="K103" s="11"/>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="17"/>
+      <c r="B104" s="18">
+        <v>10076</v>
+      </c>
+      <c r="C104" s="18">
+        <v>10076</v>
+      </c>
+      <c r="D104" s="18">
+        <v>1</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G104" s="13"/>
+      <c r="H104" s="13"/>
+      <c r="I104" s="13"/>
+      <c r="J104" s="13"/>
+      <c r="K104" s="14"/>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="15"/>
+      <c r="B105" s="16">
+        <v>10077</v>
+      </c>
+      <c r="C105" s="16">
+        <v>10077</v>
+      </c>
+      <c r="D105" s="16">
+        <v>1</v>
+      </c>
+      <c r="E105" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="G105" s="10"/>
+      <c r="H105" s="10"/>
+      <c r="I105" s="10"/>
+      <c r="J105" s="10"/>
+      <c r="K105" s="11"/>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="17"/>
+      <c r="B106" s="18">
+        <v>10078</v>
+      </c>
+      <c r="C106" s="18">
+        <v>10078</v>
+      </c>
+      <c r="D106" s="18">
+        <v>1</v>
+      </c>
+      <c r="E106" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="F106" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G106" s="13"/>
+      <c r="H106" s="13"/>
+      <c r="I106" s="13"/>
+      <c r="J106" s="13"/>
+      <c r="K106" s="14"/>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="15"/>
+      <c r="B107" s="16">
+        <v>10079</v>
+      </c>
+      <c r="C107" s="16">
+        <v>10079</v>
+      </c>
+      <c r="D107" s="16">
+        <v>1</v>
+      </c>
+      <c r="E107" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="G107" s="10"/>
+      <c r="H107" s="10"/>
+      <c r="I107" s="10"/>
+      <c r="J107" s="10"/>
+      <c r="K107" s="11"/>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="17"/>
+      <c r="B108" s="18">
+        <v>10080</v>
+      </c>
+      <c r="C108" s="18">
+        <v>10080</v>
+      </c>
+      <c r="D108" s="18">
+        <v>1</v>
+      </c>
+      <c r="E108" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="F108" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="G108" s="13"/>
+      <c r="H108" s="13"/>
+      <c r="I108" s="13"/>
+      <c r="J108" s="13"/>
+      <c r="K108" s="14"/>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="15"/>
+      <c r="B109" s="16">
+        <v>10081</v>
+      </c>
+      <c r="C109" s="16">
+        <v>10081</v>
+      </c>
+      <c r="D109" s="16">
+        <v>1</v>
+      </c>
+      <c r="E109" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="F109" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="G109" s="10"/>
+      <c r="H109" s="10"/>
+      <c r="I109" s="10"/>
+      <c r="J109" s="10"/>
+      <c r="K109" s="11"/>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="17"/>
+      <c r="B110" s="18">
+        <v>10082</v>
+      </c>
+      <c r="C110" s="18">
+        <v>10082</v>
+      </c>
+      <c r="D110" s="18">
+        <v>1</v>
+      </c>
+      <c r="E110" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F110" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
+      <c r="I110" s="13"/>
+      <c r="J110" s="13"/>
+      <c r="K110" s="14"/>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="15"/>
+      <c r="B111" s="16">
+        <v>10083</v>
+      </c>
+      <c r="C111" s="16">
+        <v>10083</v>
+      </c>
+      <c r="D111" s="16">
+        <v>1</v>
+      </c>
+      <c r="E111" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F111" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G111" s="10"/>
+      <c r="H111" s="10"/>
+      <c r="I111" s="10"/>
+      <c r="J111" s="10"/>
+      <c r="K111" s="11"/>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" s="17"/>
+      <c r="B112" s="18">
+        <v>10084</v>
+      </c>
+      <c r="C112" s="18">
+        <v>10084</v>
+      </c>
+      <c r="D112" s="18">
+        <v>1</v>
+      </c>
+      <c r="E112" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="F112" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="13"/>
+      <c r="J112" s="13"/>
+      <c r="K112" s="14"/>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" s="15"/>
+      <c r="B113" s="16">
+        <v>10085</v>
+      </c>
+      <c r="C113" s="16">
+        <v>10085</v>
+      </c>
+      <c r="D113" s="16">
+        <v>1</v>
+      </c>
+      <c r="E113" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F113" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="G113" s="10"/>
+      <c r="H113" s="10"/>
+      <c r="I113" s="10"/>
+      <c r="J113" s="10"/>
+      <c r="K113" s="11"/>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" s="17"/>
+      <c r="B114" s="18">
+        <v>10086</v>
+      </c>
+      <c r="C114" s="18">
+        <v>10086</v>
+      </c>
+      <c r="D114" s="18">
+        <v>1</v>
+      </c>
+      <c r="E114" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F114" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
+      <c r="I114" s="13"/>
+      <c r="J114" s="13"/>
+      <c r="K114" s="14"/>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" s="15"/>
+      <c r="B115" s="16">
+        <v>10087</v>
+      </c>
+      <c r="C115" s="16">
+        <v>10087</v>
+      </c>
+      <c r="D115" s="16">
+        <v>1</v>
+      </c>
+      <c r="E115" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="F115" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="G115" s="10"/>
+      <c r="H115" s="10"/>
+      <c r="I115" s="10"/>
+      <c r="J115" s="10"/>
+      <c r="K115" s="11"/>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" s="17"/>
+      <c r="B116" s="18">
+        <v>10088</v>
+      </c>
+      <c r="C116" s="18">
+        <v>10088</v>
+      </c>
+      <c r="D116" s="18">
+        <v>1</v>
+      </c>
+      <c r="E116" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F116" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="G116" s="13"/>
+      <c r="H116" s="13"/>
+      <c r="I116" s="13"/>
+      <c r="J116" s="13"/>
+      <c r="K116" s="14"/>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" s="15"/>
+      <c r="B117" s="16">
+        <v>10089</v>
+      </c>
+      <c r="C117" s="16">
+        <v>10089</v>
+      </c>
+      <c r="D117" s="16">
+        <v>1</v>
+      </c>
+      <c r="E117" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F117" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="G117" s="10"/>
+      <c r="H117" s="10"/>
+      <c r="I117" s="10"/>
+      <c r="J117" s="10"/>
+      <c r="K117" s="11"/>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="17"/>
+      <c r="B118" s="18">
+        <v>10090</v>
+      </c>
+      <c r="C118" s="18">
+        <v>10090</v>
+      </c>
+      <c r="D118" s="18">
+        <v>1</v>
+      </c>
+      <c r="E118" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="F118" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="G118" s="13"/>
+      <c r="H118" s="13"/>
+      <c r="I118" s="13"/>
+      <c r="J118" s="13"/>
+      <c r="K118" s="14"/>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="15"/>
+      <c r="B119" s="16">
+        <v>10091</v>
+      </c>
+      <c r="C119" s="16">
+        <v>10091</v>
+      </c>
+      <c r="D119" s="16">
+        <v>1</v>
+      </c>
+      <c r="E119" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="F119" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="G119" s="10"/>
+      <c r="H119" s="10"/>
+      <c r="I119" s="10"/>
+      <c r="J119" s="10"/>
+      <c r="K119" s="11"/>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="17"/>
+      <c r="B120" s="18">
+        <v>10092</v>
+      </c>
+      <c r="C120" s="18">
+        <v>10092</v>
+      </c>
+      <c r="D120" s="18">
+        <v>1</v>
+      </c>
+      <c r="E120" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="F120" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
+      <c r="I120" s="13"/>
+      <c r="J120" s="13"/>
+      <c r="K120" s="14"/>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" s="15"/>
+      <c r="B121" s="16">
+        <v>10093</v>
+      </c>
+      <c r="C121" s="16">
+        <v>10093</v>
+      </c>
+      <c r="D121" s="16">
+        <v>1</v>
+      </c>
+      <c r="E121" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="F121" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G121" s="10"/>
+      <c r="H121" s="10"/>
+      <c r="I121" s="10"/>
+      <c r="J121" s="10"/>
+      <c r="K121" s="11"/>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" s="17"/>
+      <c r="B122" s="18">
+        <v>10094</v>
+      </c>
+      <c r="C122" s="18">
+        <v>10094</v>
+      </c>
+      <c r="D122" s="18">
+        <v>1</v>
+      </c>
+      <c r="E122" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F122" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="13"/>
+      <c r="J122" s="13"/>
+      <c r="K122" s="14"/>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="15"/>
+      <c r="B123" s="16">
+        <v>10095</v>
+      </c>
+      <c r="C123" s="16">
+        <v>10095</v>
+      </c>
+      <c r="D123" s="16">
+        <v>1</v>
+      </c>
+      <c r="E123" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="F123" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="G123" s="10"/>
+      <c r="H123" s="10"/>
+      <c r="I123" s="10"/>
+      <c r="J123" s="10"/>
+      <c r="K123" s="11"/>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="17"/>
+      <c r="B124" s="18">
+        <v>10096</v>
+      </c>
+      <c r="C124" s="18">
+        <v>10096</v>
+      </c>
+      <c r="D124" s="18">
+        <v>1</v>
+      </c>
+      <c r="E124" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="F124" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="G124" s="13"/>
+      <c r="H124" s="13"/>
+      <c r="I124" s="13"/>
+      <c r="J124" s="13"/>
+      <c r="K124" s="14"/>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="15"/>
+      <c r="B125" s="16">
+        <v>10097</v>
+      </c>
+      <c r="C125" s="16">
+        <v>10097</v>
+      </c>
+      <c r="D125" s="16">
+        <v>1</v>
+      </c>
+      <c r="E125" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="F125" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="G125" s="10"/>
+      <c r="H125" s="10"/>
+      <c r="I125" s="10"/>
+      <c r="J125" s="10"/>
+      <c r="K125" s="11"/>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="17"/>
+      <c r="B126" s="18">
+        <v>10098</v>
+      </c>
+      <c r="C126" s="18">
+        <v>10098</v>
+      </c>
+      <c r="D126" s="18">
+        <v>1</v>
+      </c>
+      <c r="E126" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="F126" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
+      <c r="I126" s="13"/>
+      <c r="J126" s="13"/>
+      <c r="K126" s="14"/>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" s="15"/>
+      <c r="B127" s="16">
+        <v>10099</v>
+      </c>
+      <c r="C127" s="16">
+        <v>10099</v>
+      </c>
+      <c r="D127" s="16">
+        <v>1</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="F127" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G127" s="10"/>
+      <c r="H127" s="10"/>
+      <c r="I127" s="10"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="11"/>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" s="17"/>
+      <c r="B128" s="18">
+        <v>10100</v>
+      </c>
+      <c r="C128" s="18">
+        <v>10100</v>
+      </c>
+      <c r="D128" s="18">
+        <v>1</v>
+      </c>
+      <c r="E128" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="F128" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G128" s="13"/>
+      <c r="H128" s="13"/>
+      <c r="I128" s="13"/>
+      <c r="J128" s="13"/>
+      <c r="K128" s="14"/>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" s="19"/>
+      <c r="B129" s="20"/>
+      <c r="C129" s="20"/>
+      <c r="D129" s="20"/>
+      <c r="E129" s="20"/>
+      <c r="F129" s="20"/>
+      <c r="G129" s="20"/>
+      <c r="H129" s="20"/>
+      <c r="I129" s="20"/>
+      <c r="J129" s="20"/>
+      <c r="K129" s="21"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>